--- a/api/src/main/resources/importaciones/Dinardap/clientes.xlsx
+++ b/api/src/main/resources/importaciones/Dinardap/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismael\Documents\calero-app-desktop\api\src\main\resources\importaciones\Dinardap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238BFA05-A184-4FC4-9ACB-CC21FCEF6F24}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5CA407-4DC7-4E94-9A34-71C0BD9BF8CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="120" windowWidth="18915" windowHeight="8475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
